--- a/Figuras/AGREGADOR ANALYSIS/AGREGADOR ANALYSIS_sensibilidade.xlsx
+++ b/Figuras/AGREGADOR ANALYSIS/AGREGADOR ANALYSIS_sensibilidade.xlsx
@@ -425,101 +425,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Parametro variado</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Preco Diesel [R$]</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Cotacao Dolar</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Preco Razao Elepot [USD]</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preco R.E. Cor. Dolar [R$]</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Preco Bat [USD]</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Preco Bat Cor. Dolar [R$]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Preco UC [USD]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Preco UC Cor. Dolar [R$]</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>C-rate</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Nm,b</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Np,b</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nm,uc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Np,uc</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Volume Total [L]</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Energia Total Bat. [kWh]</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Energia Total UC. [kWh]</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Energia Total [kWh]</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Pth [kW]</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>VPL [R$]</t>
         </is>
@@ -529,186 +534,804 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Preco Diesel</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>3.69</v>
       </c>
-      <c r="C2" t="n">
-        <v>4.58</v>
-      </c>
       <c r="D2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>53</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J2" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>28</v>
+      </c>
+      <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.312</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="I2" t="n">
-        <v>26.793</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M2" t="n">
-        <v>19</v>
-      </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>1409.536</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>270.336</v>
+        <v>1335.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.1856</v>
+        <v>286.72</v>
       </c>
       <c r="R2" t="n">
-        <v>271.5216</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>550</v>
+        <v>286.72</v>
       </c>
       <c r="T2" t="n">
-        <v>3084956.916366747</v>
+        <v>1050</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5022550.245888729</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
-        <v>3.69</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Preco Diesel</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>4.58</v>
+        <v>7.46</v>
       </c>
       <c r="D3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>53</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J3" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>28</v>
+      </c>
+      <c r="M3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>29.312</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="I3" t="n">
-        <v>26.793</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M3" t="n">
-        <v>9</v>
-      </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="O3" t="n">
-        <v>1287.168</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>245.76</v>
+        <v>1335.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.1232</v>
+        <v>286.72</v>
       </c>
       <c r="R3" t="n">
-        <v>246.8832</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1550</v>
+        <v>286.72</v>
       </c>
       <c r="T3" t="n">
-        <v>6404152.218272088</v>
+        <v>1000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>10783384.85291664</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
-        <v>3.69</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cotacao Dolar</t>
+        </is>
       </c>
       <c r="C4" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D4" t="n">
         <v>4.58</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>58.624</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J4" t="n">
+        <v>44.655</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>27</v>
+      </c>
+      <c r="M4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="N4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1374.656</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="S4" t="n">
+        <v>277.1664</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1525</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8307894.819695824</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cotacao Dolar</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>63.09999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>80.768</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J5" t="n">
+        <v>61.52249999999999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1163.264</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>229.376</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.7487999999999999</v>
+      </c>
+      <c r="S5" t="n">
+        <v>230.1248</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1325</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7651920.10600846</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Preco Razao Elepot</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J6" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>27</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1374.656</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="S6" t="n">
+        <v>277.1664</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1525</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8278071.582609762</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Preco Razao Elepot</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="n">
+        <v>106</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J7" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>27</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1374.656</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="S7" t="n">
+        <v>277.1664</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1525</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8119071.582609762</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Preco Bat</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>53</v>
+      </c>
+      <c r="G8" t="n">
         <v>6.4</v>
       </c>
-      <c r="G4" t="n">
-        <v>29.312</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="H8" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>28</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1325</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8471241.748582251</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Preco Bat</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>34.688</v>
+      </c>
+      <c r="H9" t="n">
+        <v>183.8464</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1390.528</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8111999999999999</v>
+      </c>
+      <c r="S9" t="n">
+        <v>277.2912</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1525</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7376041.248988453</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Preco UC</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>53</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I10" t="n">
         <v>5.85</v>
       </c>
-      <c r="I4" t="n">
-        <v>26.793</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="J10" t="n">
+        <v>31.005</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>28</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8216222.481615079</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Preco UC</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E11" t="n">
         <v>10</v>
       </c>
-      <c r="K4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="F11" t="n">
+        <v>53</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I11" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="J11" t="n">
+        <v>72.345</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>27</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>15</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1406.4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.9359999999999999</v>
+      </c>
+      <c r="S11" t="n">
+        <v>277.416</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1225</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7951958.046693672</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M4" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C-rate</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E12" t="n">
         <v>10</v>
       </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1223.68</v>
-      </c>
-      <c r="P4" t="n">
-        <v>245.76</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="R4" t="n">
-        <v>246.384</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1675</v>
-      </c>
-      <c r="T4" t="n">
-        <v>6568673.825787353</v>
+      <c r="F12" t="n">
+        <v>53</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>28</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>13</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3913775.475460147</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C-rate</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>53</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" t="n">
+        <v>28</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1525</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8304834.573260609</v>
       </c>
     </row>
   </sheetData>

--- a/Figuras/AGREGADOR ANALYSIS/AGREGADOR ANALYSIS_sensibilidade.xlsx
+++ b/Figuras/AGREGADOR ANALYSIS/AGREGADOR ANALYSIS_sensibilidade.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,50 +481,60 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Nm_b min</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Nm_uc min</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Nm,b</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Np,b</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Nm,uc</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Np,uc</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Volume Total [L]</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Energia Total Bat. [kWh]</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Energia Total UC. [kWh]</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Energia Total [kWh]</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Pth [kW]</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>VPL [R$]</t>
         </is>
@@ -567,33 +577,39 @@
         <v>6</v>
       </c>
       <c r="L2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11</v>
+      </c>
+      <c r="N2" t="n">
         <v>28</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>13</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>1335.04</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>286.72</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>286.72</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="V2" t="n">
         <v>1050</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>5022550.245888729</v>
       </c>
     </row>
@@ -634,33 +650,39 @@
         <v>6</v>
       </c>
       <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="n">
         <v>28</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>5</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>26</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>1335.04</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>286.72</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>286.72</v>
       </c>
       <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="V3" t="n">
         <v>1000</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>10783384.85291664</v>
       </c>
     </row>
@@ -701,33 +723,39 @@
         <v>6</v>
       </c>
       <c r="L4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="n">
         <v>27</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="N4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>1374.656</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>276.48</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.6864</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>277.1664</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>1525</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>8307894.819695824</v>
       </c>
     </row>
@@ -768,33 +796,39 @@
         <v>6</v>
       </c>
       <c r="L5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="n">
         <v>28</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>12</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>1163.264</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>229.376</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.7487999999999999</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>230.1248</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>1325</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>7651920.10600846</v>
       </c>
     </row>
@@ -835,33 +869,39 @@
         <v>6</v>
       </c>
       <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
         <v>27</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="N6" t="n">
-        <v>11</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>1374.656</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>276.48</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.6864</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>277.1664</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>1525</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>8278071.582609762</v>
       </c>
     </row>
@@ -902,33 +942,39 @@
         <v>6</v>
       </c>
       <c r="L7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="n">
         <v>27</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="n">
-        <v>11</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>1374.656</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>276.48</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>0.6864</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>277.1664</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>1525</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>8119071.582609762</v>
       </c>
     </row>
@@ -969,33 +1015,39 @@
         <v>6</v>
       </c>
       <c r="L8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="n">
         <v>28</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>5</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>14</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>1335.04</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>286.72</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>286.72</v>
       </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="V8" t="n">
         <v>1325</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>8471241.748582251</v>
       </c>
     </row>
@@ -1036,33 +1088,39 @@
         <v>6</v>
       </c>
       <c r="L9" t="n">
+        <v>15</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="n">
         <v>27</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>13</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>1390.528</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>276.48</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>0.8111999999999999</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>277.2912</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>1525</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>7376041.248988453</v>
       </c>
     </row>
@@ -1103,33 +1161,39 @@
         <v>6</v>
       </c>
       <c r="L10" t="n">
+        <v>15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="n">
         <v>28</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>26</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>1335.04</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>286.72</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>286.72</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="V10" t="n">
         <v>1000</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>8216222.481615079</v>
       </c>
     </row>
@@ -1170,33 +1234,39 @@
         <v>6</v>
       </c>
       <c r="L11" t="n">
+        <v>15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="n">
         <v>27</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>15</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>1406.4</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>276.48</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.9359999999999999</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>277.416</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>1225</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>7951958.046693672</v>
       </c>
     </row>
@@ -1237,33 +1307,39 @@
         <v>2</v>
       </c>
       <c r="L12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="n">
         <v>28</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>5</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>13</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>1335.04</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>286.72</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>286.72</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="V12" t="n">
         <v>1000</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>3913775.475460147</v>
       </c>
     </row>
@@ -1304,34 +1380,332 @@
         <v>10</v>
       </c>
       <c r="L13" t="n">
+        <v>15</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="n">
         <v>28</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>5</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>14</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>1335.04</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>286.72</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>286.72</v>
       </c>
       <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="V13" t="n">
         <v>1525</v>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>8304834.573260609</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nm_b min</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>53</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>27</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1374.656</v>
+      </c>
+      <c r="S14" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="U14" t="n">
+        <v>277.1664</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1525</v>
+      </c>
+      <c r="W14" t="n">
+        <v>8225071.582609762</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nm_b min</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>53</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I15" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>27</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1374.656</v>
+      </c>
+      <c r="S15" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="U15" t="n">
+        <v>277.1664</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1525</v>
+      </c>
+      <c r="W15" t="n">
+        <v>8225071.582609762</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nm_uc min</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>53</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>27</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1374.656</v>
+      </c>
+      <c r="S16" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="U16" t="n">
+        <v>277.1664</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1525</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8225071.582609762</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nm_uc min</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J17" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>15</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18</v>
+      </c>
+      <c r="N17" t="n">
+        <v>27</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1374.656</v>
+      </c>
+      <c r="S17" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="U17" t="n">
+        <v>277.1664</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1525</v>
+      </c>
+      <c r="W17" t="n">
+        <v>8225071.582609762</v>
       </c>
     </row>
   </sheetData>

--- a/Figuras/AGREGADOR ANALYSIS/AGREGADOR ANALYSIS_sensibilidade.xlsx
+++ b/Figuras/AGREGADOR ANALYSIS/AGREGADOR ANALYSIS_sensibilidade.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,11 +546,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Preco Diesel</t>
+          <t>Caso base</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.69</v>
+        <v>5.78</v>
       </c>
       <c r="D2" t="n">
         <v>5.3</v>
@@ -583,34 +583,34 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O2" t="n">
         <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1335.04</v>
+        <v>1374.656</v>
       </c>
       <c r="S2" t="n">
-        <v>286.72</v>
+        <v>276.48</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.6864</v>
       </c>
       <c r="U2" t="n">
-        <v>286.72</v>
+        <v>277.1664</v>
       </c>
       <c r="V2" t="n">
-        <v>1050</v>
+        <v>1525</v>
       </c>
       <c r="W2" t="n">
-        <v>5022550.245888729</v>
+        <v>8225071.582609762</v>
       </c>
     </row>
     <row r="3">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.46</v>
+        <v>3.69</v>
       </c>
       <c r="D3" t="n">
         <v>5.3</v>
@@ -662,7 +662,7 @@
         <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>286.72</v>
       </c>
       <c r="V3" t="n">
-        <v>1000</v>
+        <v>1150</v>
       </c>
       <c r="W3" t="n">
-        <v>10783384.85291664</v>
+        <v>5022550.245888729</v>
       </c>
     </row>
     <row r="4">
@@ -692,32 +692,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cotacao Dolar</t>
+          <t>Preco Diesel</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.78</v>
+        <v>7.46</v>
       </c>
       <c r="D4" t="n">
-        <v>4.58</v>
+        <v>5.3</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>45.8</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>12.8</v>
       </c>
       <c r="H4" t="n">
-        <v>58.624</v>
+        <v>67.84</v>
       </c>
       <c r="I4" t="n">
         <v>9.75</v>
       </c>
       <c r="J4" t="n">
-        <v>44.655</v>
+        <v>51.675</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
@@ -729,34 +729,34 @@
         <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1374.656</v>
+        <v>1335.04</v>
       </c>
       <c r="S4" t="n">
-        <v>276.48</v>
+        <v>286.72</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6864</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>277.1664</v>
+        <v>286.72</v>
       </c>
       <c r="V4" t="n">
-        <v>1525</v>
+        <v>1100</v>
       </c>
       <c r="W4" t="n">
-        <v>8307894.819695824</v>
+        <v>10783384.85291664</v>
       </c>
     </row>
     <row r="5">
@@ -772,25 +772,25 @@
         <v>5.78</v>
       </c>
       <c r="D5" t="n">
-        <v>6.31</v>
+        <v>4.58</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>63.09999999999999</v>
+        <v>45.8</v>
       </c>
       <c r="G5" t="n">
         <v>12.8</v>
       </c>
       <c r="H5" t="n">
-        <v>80.768</v>
+        <v>58.624</v>
       </c>
       <c r="I5" t="n">
         <v>9.75</v>
       </c>
       <c r="J5" t="n">
-        <v>61.52249999999999</v>
+        <v>44.655</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
@@ -802,34 +802,34 @@
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1163.264</v>
+        <v>1374.656</v>
       </c>
       <c r="S5" t="n">
-        <v>229.376</v>
+        <v>276.48</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7487999999999999</v>
+        <v>0.6864</v>
       </c>
       <c r="U5" t="n">
-        <v>230.1248</v>
+        <v>277.1664</v>
       </c>
       <c r="V5" t="n">
-        <v>1325</v>
+        <v>1525</v>
       </c>
       <c r="W5" t="n">
-        <v>7651920.10600846</v>
+        <v>8307894.819695824</v>
       </c>
     </row>
     <row r="6">
@@ -838,32 +838,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Preco Razao Elepot</t>
+          <t>Cotacao Dolar</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5.78</v>
       </c>
       <c r="D6" t="n">
-        <v>5.3</v>
+        <v>6.31</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>26.5</v>
+        <v>63.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>12.8</v>
       </c>
       <c r="H6" t="n">
-        <v>67.84</v>
+        <v>80.768</v>
       </c>
       <c r="I6" t="n">
         <v>9.75</v>
       </c>
       <c r="J6" t="n">
-        <v>51.675</v>
+        <v>61.52249999999999</v>
       </c>
       <c r="K6" t="n">
         <v>6</v>
@@ -875,34 +875,34 @@
         <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1374.656</v>
+        <v>1179.136</v>
       </c>
       <c r="S6" t="n">
-        <v>276.48</v>
+        <v>229.376</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6864</v>
+        <v>0.8735999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>277.1664</v>
+        <v>230.2496</v>
       </c>
       <c r="V6" t="n">
-        <v>1525</v>
+        <v>1325</v>
       </c>
       <c r="W6" t="n">
-        <v>8278071.582609762</v>
+        <v>7653783.249863784</v>
       </c>
     </row>
     <row r="7">
@@ -921,10 +921,10 @@
         <v>5.3</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>26.5</v>
       </c>
       <c r="G7" t="n">
         <v>12.8</v>
@@ -975,7 +975,7 @@
         <v>1525</v>
       </c>
       <c r="W7" t="n">
-        <v>8119071.582609762</v>
+        <v>8278071.582609762</v>
       </c>
     </row>
     <row r="8">
@@ -984,7 +984,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Preco Bat</t>
+          <t>Preco Razao Elepot</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -994,16 +994,16 @@
         <v>5.3</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>12.8</v>
       </c>
       <c r="H8" t="n">
-        <v>33.92</v>
+        <v>67.84</v>
       </c>
       <c r="I8" t="n">
         <v>9.75</v>
@@ -1021,34 +1021,34 @@
         <v>11</v>
       </c>
       <c r="N8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O8" t="n">
         <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1335.04</v>
+        <v>1374.656</v>
       </c>
       <c r="S8" t="n">
-        <v>286.72</v>
+        <v>276.48</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.6864</v>
       </c>
       <c r="U8" t="n">
-        <v>286.72</v>
+        <v>277.1664</v>
       </c>
       <c r="V8" t="n">
-        <v>1325</v>
+        <v>1525</v>
       </c>
       <c r="W8" t="n">
-        <v>8471241.748582251</v>
+        <v>8119071.582609762</v>
       </c>
     </row>
     <row r="9">
@@ -1073,10 +1073,10 @@
         <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>34.688</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>183.8464</v>
+        <v>33.92</v>
       </c>
       <c r="I9" t="n">
         <v>9.75</v>
@@ -1094,34 +1094,34 @@
         <v>11</v>
       </c>
       <c r="N9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O9" t="n">
         <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1390.528</v>
+        <v>1335.04</v>
       </c>
       <c r="S9" t="n">
-        <v>276.48</v>
+        <v>286.72</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8111999999999999</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>277.2912</v>
+        <v>286.72</v>
       </c>
       <c r="V9" t="n">
-        <v>1525</v>
+        <v>1275</v>
       </c>
       <c r="W9" t="n">
-        <v>7376041.248988453</v>
+        <v>8471241.748582251</v>
       </c>
     </row>
     <row r="10">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Preco UC</t>
+          <t>Preco Bat</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1146,16 +1146,16 @@
         <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>12.8</v>
+        <v>34.688</v>
       </c>
       <c r="H10" t="n">
-        <v>67.84</v>
+        <v>183.8464</v>
       </c>
       <c r="I10" t="n">
-        <v>5.85</v>
+        <v>9.75</v>
       </c>
       <c r="J10" t="n">
-        <v>31.005</v>
+        <v>51.675</v>
       </c>
       <c r="K10" t="n">
         <v>6</v>
@@ -1167,34 +1167,34 @@
         <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O10" t="n">
         <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1335.04</v>
+        <v>1374.656</v>
       </c>
       <c r="S10" t="n">
-        <v>286.72</v>
+        <v>276.48</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.6864</v>
       </c>
       <c r="U10" t="n">
-        <v>286.72</v>
+        <v>277.1664</v>
       </c>
       <c r="V10" t="n">
-        <v>1000</v>
+        <v>1525</v>
       </c>
       <c r="W10" t="n">
-        <v>8216222.481615079</v>
+        <v>7379346.193788972</v>
       </c>
     </row>
     <row r="11">
@@ -1225,10 +1225,10 @@
         <v>67.84</v>
       </c>
       <c r="I11" t="n">
-        <v>13.65</v>
+        <v>5.85</v>
       </c>
       <c r="J11" t="n">
-        <v>72.345</v>
+        <v>31.005</v>
       </c>
       <c r="K11" t="n">
         <v>6</v>
@@ -1240,34 +1240,34 @@
         <v>11</v>
       </c>
       <c r="N11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O11" t="n">
         <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1406.4</v>
+        <v>1335.04</v>
       </c>
       <c r="S11" t="n">
-        <v>276.48</v>
+        <v>286.72</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9359999999999999</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>277.416</v>
+        <v>286.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1225</v>
+        <v>1100</v>
       </c>
       <c r="W11" t="n">
-        <v>7951958.046693672</v>
+        <v>8216222.481615079</v>
       </c>
     </row>
     <row r="12">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C-rate</t>
+          <t>Preco UC</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1298,13 +1298,13 @@
         <v>67.84</v>
       </c>
       <c r="I12" t="n">
-        <v>9.75</v>
+        <v>13.65</v>
       </c>
       <c r="J12" t="n">
-        <v>51.675</v>
+        <v>72.345</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>15</v>
@@ -1313,34 +1313,34 @@
         <v>11</v>
       </c>
       <c r="N12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1335.04</v>
+        <v>1374.656</v>
       </c>
       <c r="S12" t="n">
-        <v>286.72</v>
+        <v>276.48</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.6864</v>
       </c>
       <c r="U12" t="n">
-        <v>286.72</v>
+        <v>277.1664</v>
       </c>
       <c r="V12" t="n">
-        <v>1000</v>
+        <v>1525</v>
       </c>
       <c r="W12" t="n">
-        <v>3913775.475460147</v>
+        <v>8221433.662609762</v>
       </c>
     </row>
     <row r="13">
@@ -1377,7 +1377,7 @@
         <v>51.675</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>15</v>
@@ -1392,7 +1392,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1410,10 +1410,10 @@
         <v>286.72</v>
       </c>
       <c r="V13" t="n">
-        <v>1525</v>
+        <v>1050</v>
       </c>
       <c r="W13" t="n">
-        <v>8304834.573260609</v>
+        <v>3913775.475460147</v>
       </c>
     </row>
     <row r="14">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nm_b min</t>
+          <t>C-rate</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1450,10 +1450,10 @@
         <v>51.675</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
         <v>11</v>
@@ -1465,28 +1465,28 @@
         <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1374.656</v>
+        <v>1287.36</v>
       </c>
       <c r="S14" t="n">
         <v>276.48</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6864</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>277.1664</v>
+        <v>276.48</v>
       </c>
       <c r="V14" t="n">
-        <v>1525</v>
+        <v>1400</v>
       </c>
       <c r="W14" t="n">
-        <v>8225071.582609762</v>
+        <v>8320296.856422562</v>
       </c>
     </row>
     <row r="15">
@@ -1526,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
         <v>11</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nm_uc min</t>
+          <t>Nm_b min</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1599,10 +1599,10 @@
         <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N16" t="n">
         <v>27</v>
@@ -1675,7 +1675,7 @@
         <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
         <v>27</v>
@@ -1705,6 +1705,79 @@
         <v>1525</v>
       </c>
       <c r="W17" t="n">
+        <v>8225071.582609762</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nm_uc min</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J18" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>15</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18</v>
+      </c>
+      <c r="N18" t="n">
+        <v>27</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1374.656</v>
+      </c>
+      <c r="S18" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="U18" t="n">
+        <v>277.1664</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1525</v>
+      </c>
+      <c r="W18" t="n">
         <v>8225071.582609762</v>
       </c>
     </row>
